--- a/artfynd/A 21938-2021 artfynd.xlsx
+++ b/artfynd/A 21938-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119821089</v>
+        <v>119821026</v>
       </c>
       <c r="B2" t="n">
         <v>57310</v>
@@ -709,14 +709,9 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552431</v>
+        <v>552460</v>
       </c>
       <c r="R2" t="n">
-        <v>7064205</v>
+        <v>7064184</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119821026</v>
+        <v>119821089</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -831,9 +826,14 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552460</v>
+        <v>552431</v>
       </c>
       <c r="R3" t="n">
-        <v>7064184</v>
+        <v>7064205</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 21938-2021 artfynd.xlsx
+++ b/artfynd/A 21938-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119821026</v>
+        <v>119821089</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,9 +709,14 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552460</v>
+        <v>552431</v>
       </c>
       <c r="R2" t="n">
-        <v>7064184</v>
+        <v>7064205</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +770,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119821089</v>
+        <v>119821026</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,14 +831,9 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552431</v>
+        <v>552460</v>
       </c>
       <c r="R3" t="n">
-        <v>7064205</v>
+        <v>7064184</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
